--- a/public/documents/requirement6/6_1/6_1_modelo_riscos_oportunidades.xlsx
+++ b/public/documents/requirement6/6_1/6_1_modelo_riscos_oportunidades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement6\6_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AEFEAE-0DC2-4A9C-8501-F9463F9AF41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81CC09F-16B8-4074-B1F6-20B23FF1A87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
   </bookViews>
@@ -290,7 +290,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,12 +350,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="0"/>
@@ -364,7 +358,7 @@
     </font>
     <font>
       <b/>
-      <sz val="65"/>
+      <sz val="50"/>
       <color theme="0"/>
       <name val="Cambria"/>
       <family val="1"/>
@@ -442,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -462,17 +456,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -480,7 +471,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -490,44 +481,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -561,15 +548,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>107577</xdr:colOff>
+      <xdr:colOff>71718</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>80682</xdr:rowOff>
+      <xdr:rowOff>26895</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>259977</xdr:colOff>
+      <xdr:colOff>98611</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>80681</xdr:rowOff>
+      <xdr:rowOff>161364</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -598,8 +585,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="107577" y="80682"/>
-          <a:ext cx="1317812" cy="1317811"/>
+          <a:off x="71718" y="26895"/>
+          <a:ext cx="1192305" cy="1192304"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1061,85 +1048,85 @@
     <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="26" t="s">
+    <row r="2" spans="2:18" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-    </row>
-    <row r="4" spans="2:18" s="29" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="27" t="s">
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+    </row>
+    <row r="4" spans="2:18" s="22" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="2:18" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:18" s="29" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="30" t="s">
+    <row r="6" spans="2:18" s="22" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="30" t="s">
+      <c r="M6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="30" t="s">
+      <c r="N6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="30" t="s">
+      <c r="O6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="30" t="s">
+      <c r="P6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="Q6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="R6" s="30" t="s">
+      <c r="R6" s="23" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1160,7 +1147,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="11"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
@@ -1286,121 +1273,50 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
     </row>
     <row r="25" spans="2:11" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
@@ -1423,238 +1339,236 @@
   <dimension ref="B2:G22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.21875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="1.88671875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="1.44140625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="38.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="13"/>
+    <col min="1" max="1" width="3.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.21875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="1.88671875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.44140625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="38.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="4" spans="2:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="26" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="4.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>37</v>
       </c>
       <c r="E19"/>
     </row>
     <row r="20" spans="2:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E20"/>
     </row>
     <row r="21" spans="2:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E21"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1672,163 +1586,163 @@
   <dimension ref="B2:I10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="16"/>
-    <col min="3" max="3" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.88671875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="16"/>
-    <col min="6" max="6" width="12.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.44140625" style="16" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="2.6640625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="15"/>
+    <col min="3" max="3" width="11.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.88671875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="15"/>
+    <col min="6" max="6" width="12.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.44140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="15" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="E4" s="25" t="s">
+      <c r="C4" s="24"/>
+      <c r="E4" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="H4" s="25" t="s">
+      <c r="F4" s="24"/>
+      <c r="H4" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="23">
+      <c r="B6" s="18">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="19" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="23">
+      <c r="E6" s="18">
         <v>1</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="19" t="s">
         <v>48</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="19" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="23">
+      <c r="B7" s="18">
         <v>2</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="19" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="23">
+      <c r="E7" s="18">
         <v>2</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="19" t="s">
         <v>49</v>
       </c>
       <c r="G7" s="6"/>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="23">
+      <c r="B8" s="18">
         <v>3</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="23">
+      <c r="E8" s="18">
         <v>3</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="19" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="23">
+      <c r="B9" s="18">
         <v>4</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="19" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="23">
+      <c r="E9" s="18">
         <v>4</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="19" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="6"/>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="19" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="23">
+      <c r="B10" s="18">
         <v>5</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="23">
+      <c r="E10" s="18">
         <v>5</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="19" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="6"/>

--- a/public/documents/requirement6/6_1/6_1_modelo_riscos_oportunidades.xlsx
+++ b/public/documents/requirement6/6_1/6_1_modelo_riscos_oportunidades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement6\6_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81CC09F-16B8-4074-B1F6-20B23FF1A87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C441048B-160F-44E9-9FCF-D3D0BC4A4CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz" sheetId="1" r:id="rId1"/>
@@ -290,7 +290,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,6 +360,19 @@
       <b/>
       <sz val="50"/>
       <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
     </font>
@@ -436,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -505,18 +518,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1049,24 +1063,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
     </row>
     <row r="4" spans="2:18" s="22" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="20" t="s">
@@ -1340,7 +1354,7 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="49.21875" style="12" customWidth="1"/>
     <col min="4" max="4" width="1.88671875" style="12" customWidth="1"/>
     <col min="5" max="5" width="34.88671875" style="12" bestFit="1" customWidth="1"/>
@@ -1359,17 +1373,18 @@
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
     </row>
-    <row r="4" spans="2:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="27" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1610,18 +1625,18 @@
       <c r="I2" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="E4" s="24" t="s">
+      <c r="C4" s="26"/>
+      <c r="E4" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="H4" s="24" t="s">
+      <c r="F4" s="26"/>
+      <c r="H4" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="24"/>
+      <c r="I4" s="26"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
